--- a/outputs/reports/random_forest_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/random_forest_v2/feature_importance_top10.xlsx
@@ -479,10 +479,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07143149908118701</v>
+        <v>0.07254925166059462</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07143149908118702</v>
+        <v>0.07254925166059463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.25%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0658730897024364</v>
+        <v>0.0669679439499392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06587308970243641</v>
+        <v>0.06696794394993921</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.59%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.70%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06240819698226026</v>
+        <v>0.0584006576381239</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06240819698226027</v>
+        <v>0.05840065763812391</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.24%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05227164345278072</v>
+        <v>0.05363503924955487</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05227164345278074</v>
+        <v>0.05363503924955488</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05156726898647793</v>
+        <v>0.05182978588028408</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05156726898647795</v>
+        <v>0.05182978588028409</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.18%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04990558558890892</v>
+        <v>0.05121974055824543</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04990558558890893</v>
+        <v>0.05121974055824544</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04772365960239108</v>
+        <v>0.04943349195958752</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04772365960239109</v>
+        <v>0.04943349195958754</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.77%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.94%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0428885918594519</v>
+        <v>0.04164635585885659</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04288859185945191</v>
+        <v>0.0416463558588566</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.29%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03540480263418778</v>
+        <v>0.03624704834575684</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03540480263418778</v>
+        <v>0.03624704834575685</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.62%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02928295777591394</v>
+        <v>0.03002864339537454</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02928295777591394</v>
+        <v>0.03002864339537455</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.93%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/random_forest_v2/feature_importance_top10.xlsx
+++ b/outputs/reports/random_forest_v2/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07254925166059462</v>
+        <v>0.07577859416271837</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07254925166059463</v>
+        <v>0.07577859416271837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.25%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.58%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -506,19 +506,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0669679439499392</v>
+        <v>0.0534527252886216</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06696794394993921</v>
+        <v>0.0534527252886216</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.70%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0584006576381239</v>
+        <v>0.05111454479859059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05840065763812391</v>
+        <v>0.05111454479859059</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.11%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05363503924955487</v>
+        <v>0.04893739718600483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05363503924955488</v>
+        <v>0.04893739718600483</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05182978588028408</v>
+        <v>0.04693978938910143</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05182978588028409</v>
+        <v>0.04693978938910143</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.18%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.69%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05121974055824543</v>
+        <v>0.03563919277280889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05121974055824544</v>
+        <v>0.03563919277280889</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.56%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04943349195958752</v>
+        <v>0.03229557099280434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04943349195958754</v>
+        <v>0.03229557099280434</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.94%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04164635585885659</v>
+        <v>0.03060993279263494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0416463558588566</v>
+        <v>0.03060993279263494</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.06%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03624704834575684</v>
+        <v>0.03033419722451703</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03624704834575685</v>
+        <v>0.03033419722451703</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.62%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03002864339537454</v>
+        <v>0.02997237555286862</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03002864339537455</v>
+        <v>0.02997237555286862</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
